--- a/clipMapping.xlsx
+++ b/clipMapping.xlsx
@@ -1,16 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FabianHagerstrom\Documents\UnityProjects\tree-motion-analysis\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E66A8FE-9732-400B-8202-7AFE013D0416}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-27465" yWindow="480" windowWidth="24135" windowHeight="13890" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Form A" sheetId="1" r:id="rId5"/>
-    <sheet state="visible" name="Form B" sheetId="2" r:id="rId6"/>
-    <sheet state="visible" name="Form C" sheetId="3" r:id="rId7"/>
-    <sheet state="visible" name="Form D" sheetId="4" r:id="rId8"/>
-    <sheet state="visible" name="Form E" sheetId="5" r:id="rId9"/>
+    <sheet name="Form A" sheetId="1" r:id="rId1"/>
+    <sheet name="Form B" sheetId="2" r:id="rId2"/>
+    <sheet name="Form C" sheetId="3" r:id="rId3"/>
+    <sheet name="Form D" sheetId="4" r:id="rId4"/>
+    <sheet name="Form E" sheetId="5" r:id="rId5"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -119,21 +128,23 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
@@ -144,198 +155,263 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="15">
     <dxf>
-      <font/>
       <fill>
-        <patternFill patternType="none"/>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE8F0FE"/>
+          <bgColor rgb="FFE8F0FE"/>
+        </patternFill>
       </fill>
-      <border/>
     </dxf>
     <dxf>
-      <font/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FF5B95F9"/>
           <bgColor rgb="FF5B95F9"/>
         </patternFill>
       </fill>
-      <border/>
     </dxf>
     <dxf>
-      <font/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE8F0FE"/>
+          <bgColor rgb="FFE8F0FE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFFFFFFF"/>
           <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
-      <border/>
     </dxf>
     <dxf>
-      <font/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF5B95F9"/>
+          <bgColor rgb="FF5B95F9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFE8F0FE"/>
           <bgColor rgb="FFE8F0FE"/>
         </patternFill>
       </fill>
-      <border/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF5B95F9"/>
+          <bgColor rgb="FF5B95F9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE8F0FE"/>
+          <bgColor rgb="FFE8F0FE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF5B95F9"/>
+          <bgColor rgb="FF5B95F9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE8F0FE"/>
+          <bgColor rgb="FFE8F0FE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF5B95F9"/>
+          <bgColor rgb="FF5B95F9"/>
+        </patternFill>
+      </fill>
     </dxf>
   </dxfs>
   <tableStyles count="5">
-    <tableStyle count="3" pivot="0" name="Form A-style">
-      <tableStyleElement dxfId="1" type="headerRow"/>
-      <tableStyleElement dxfId="2" type="firstRowStripe"/>
-      <tableStyleElement dxfId="3" type="secondRowStripe"/>
+    <tableStyle name="Form A-style" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
+      <tableStyleElement type="headerRow" dxfId="14"/>
+      <tableStyleElement type="firstRowStripe" dxfId="13"/>
+      <tableStyleElement type="secondRowStripe" dxfId="12"/>
     </tableStyle>
-    <tableStyle count="3" pivot="0" name="Form B-style">
-      <tableStyleElement dxfId="1" type="headerRow"/>
-      <tableStyleElement dxfId="2" type="firstRowStripe"/>
-      <tableStyleElement dxfId="3" type="secondRowStripe"/>
+    <tableStyle name="Form B-style" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
+      <tableStyleElement type="headerRow" dxfId="11"/>
+      <tableStyleElement type="firstRowStripe" dxfId="10"/>
+      <tableStyleElement type="secondRowStripe" dxfId="9"/>
     </tableStyle>
-    <tableStyle count="3" pivot="0" name="Form C-style">
-      <tableStyleElement dxfId="1" type="headerRow"/>
-      <tableStyleElement dxfId="2" type="firstRowStripe"/>
-      <tableStyleElement dxfId="3" type="secondRowStripe"/>
+    <tableStyle name="Form C-style" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF02000000}">
+      <tableStyleElement type="headerRow" dxfId="8"/>
+      <tableStyleElement type="firstRowStripe" dxfId="7"/>
+      <tableStyleElement type="secondRowStripe" dxfId="6"/>
     </tableStyle>
-    <tableStyle count="3" pivot="0" name="Form D-style">
-      <tableStyleElement dxfId="1" type="headerRow"/>
-      <tableStyleElement dxfId="2" type="firstRowStripe"/>
-      <tableStyleElement dxfId="3" type="secondRowStripe"/>
+    <tableStyle name="Form D-style" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF03000000}">
+      <tableStyleElement type="headerRow" dxfId="5"/>
+      <tableStyleElement type="firstRowStripe" dxfId="4"/>
+      <tableStyleElement type="secondRowStripe" dxfId="3"/>
     </tableStyle>
-    <tableStyle count="3" pivot="0" name="Form E-style">
-      <tableStyleElement dxfId="1" type="headerRow"/>
-      <tableStyleElement dxfId="2" type="firstRowStripe"/>
-      <tableStyleElement dxfId="3" type="secondRowStripe"/>
+    <tableStyle name="Form E-style" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF04000000}">
+      <tableStyleElement type="headerRow" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="secondRowStripe" dxfId="0"/>
     </tableStyle>
   </tableStyles>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:F29" displayName="Table_1" name="Table_1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table_1" displayName="Table_1" ref="A1:F29">
   <tableColumns count="6">
-    <tableColumn name="ClipOrder" id="1"/>
-    <tableColumn name="ClipID" id="2"/>
-    <tableColumn name="Tree" id="3"/>
-    <tableColumn name="WindModel" id="4"/>
-    <tableColumn name="Setting" id="5"/>
-    <tableColumn name="Ordered" id="6"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ClipOrder"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="ClipID"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Tree"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="WindModel"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Setting"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Ordered"/>
   </tableColumns>
-  <tableStyleInfo name="Form A-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+  <tableStyleInfo name="Form A-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:F29" displayName="Table_2" name="Table_2" id="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Table_2" displayName="Table_2" ref="A1:F29">
   <tableColumns count="6">
-    <tableColumn name="ClipOrder" id="1"/>
-    <tableColumn name="ClipID" id="2"/>
-    <tableColumn name="Tree" id="3"/>
-    <tableColumn name="WindModel" id="4"/>
-    <tableColumn name="Setting" id="5"/>
-    <tableColumn name="Ordered" id="6"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="ClipOrder"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="ClipID"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Tree"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="WindModel"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Setting"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Ordered"/>
   </tableColumns>
-  <tableStyleInfo name="Form B-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+  <tableStyleInfo name="Form B-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:F29" displayName="Table_3" name="Table_3" id="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Table_3" displayName="Table_3" ref="A1:F29">
   <tableColumns count="6">
-    <tableColumn name="ClipOrder" id="1"/>
-    <tableColumn name="ClipID" id="2"/>
-    <tableColumn name="Tree" id="3"/>
-    <tableColumn name="WindModel" id="4"/>
-    <tableColumn name="Setting" id="5"/>
-    <tableColumn name="Ordered" id="6"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="ClipOrder"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="ClipID"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Tree"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="WindModel"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Setting"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="Ordered"/>
   </tableColumns>
-  <tableStyleInfo name="Form C-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+  <tableStyleInfo name="Form C-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:F29" displayName="Table_4" name="Table_4" id="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="Table_4" displayName="Table_4" ref="A1:F29">
   <tableColumns count="6">
-    <tableColumn name="ClipOrder" id="1"/>
-    <tableColumn name="ClipID" id="2"/>
-    <tableColumn name="Tree" id="3"/>
-    <tableColumn name="WindModel" id="4"/>
-    <tableColumn name="Setting" id="5"/>
-    <tableColumn name="Ordered" id="6"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="ClipOrder"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="ClipID"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="Tree"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="WindModel"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="Setting"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0300-000006000000}" name="Ordered"/>
   </tableColumns>
-  <tableStyleInfo name="Form D-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+  <tableStyleInfo name="Form D-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:F29" displayName="Table_5" name="Table_5" id="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="Table_5" displayName="Table_5" ref="A1:F29">
   <tableColumns count="6">
-    <tableColumn name="ClipOrder" id="1"/>
-    <tableColumn name="ClipID" id="2"/>
-    <tableColumn name="Tree" id="3"/>
-    <tableColumn name="WindModel" id="4"/>
-    <tableColumn name="Setting" id="5"/>
-    <tableColumn name="Ordered" id="6"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="ClipOrder"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="ClipID"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="Tree"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="WindModel"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0400-000005000000}" name="Setting"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0400-000006000000}" name="Ordered"/>
   </tableColumns>
-  <tableStyleInfo name="Form E-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+  <tableStyleInfo name="Form E-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -525,20 +601,23 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:F29"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="14.88"/>
+    <col min="1" max="1" width="14.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -558,573 +637,574 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="B2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="2">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="D2" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="E2" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="F2" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
-        <v>2.0</v>
-      </c>
-      <c r="B3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="D3" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="E3" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="F3" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="B4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C4" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="D4" s="2">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="E4" s="2">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F4" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="B5" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C5" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="D5" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="E5" s="2">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F5" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="B6" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C6" s="2">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="D6" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="E6" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="F6" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="B7" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C7" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="D7" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="E7" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="F7" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
-        <v>7.0</v>
-      </c>
-      <c r="B8" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C8" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="D8" s="2">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="E8" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="F8" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
-        <v>8.0</v>
-      </c>
-      <c r="B9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C9" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="D9" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="E9" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="F9" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
-        <v>9.0</v>
-      </c>
-      <c r="B10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C10" s="2">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="D10" s="2">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="E10" s="2">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F10" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
-        <v>10.0</v>
-      </c>
-      <c r="B11" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C11" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="D11" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="E11" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="F11" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
-        <v>11.0</v>
-      </c>
-      <c r="B12" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C12" s="2">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="D12" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="E12" s="2">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F12" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
-        <v>12.0</v>
-      </c>
-      <c r="B13" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>17</v>
       </c>
       <c r="C13" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="D13" s="2">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="E13" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="F13" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
-        <v>13.0</v>
-      </c>
-      <c r="B14" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>18</v>
       </c>
       <c r="C14" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="D14" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="E14" s="2">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F14" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
-        <v>14.0</v>
-      </c>
-      <c r="B15" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C15" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="D15" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="E15" s="2">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F15" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
-        <v>15.0</v>
-      </c>
-      <c r="B16" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C16" s="2">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="D16" s="2">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="E16" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="F16" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
-        <v>16.0</v>
-      </c>
-      <c r="B17" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C17" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="D17" s="2">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="E17" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="F17" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
-        <v>17.0</v>
-      </c>
-      <c r="B18" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C18" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="D18" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="E18" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="F18" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
-        <v>18.0</v>
-      </c>
-      <c r="B19" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>23</v>
       </c>
       <c r="C19" s="2">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="D19" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="E19" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="F19" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
-        <v>19.0</v>
-      </c>
-      <c r="B20" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C20" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="D20" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="E20" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="F20" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
-        <v>20.0</v>
-      </c>
-      <c r="B21" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>25</v>
       </c>
       <c r="C21" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="D21" s="2">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="E21" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="F21" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
-        <v>21.0</v>
-      </c>
-      <c r="B22" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>26</v>
       </c>
       <c r="C22" s="2">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="D22" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="E22" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="F22" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
-        <v>22.0</v>
-      </c>
-      <c r="B23" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B23" s="2" t="s">
         <v>27</v>
       </c>
       <c r="C23" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="D23" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="E23" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="F23" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
-        <v>23.0</v>
-      </c>
-      <c r="B24" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C24" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="D24" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="E24" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="F24" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
-        <v>24.0</v>
-      </c>
-      <c r="B25" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B25" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C25" s="2">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="D25" s="2">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="E25" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="F25" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
-        <v>25.0</v>
-      </c>
-      <c r="B26" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C26" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="D26" s="2">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="E26" s="2">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F26" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27" s="2">
-        <v>26.0</v>
-      </c>
-      <c r="B27" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27" s="2" t="s">
         <v>31</v>
       </c>
       <c r="C27" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="D27" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="E27" s="2">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F27" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28" s="2">
-        <v>27.0</v>
-      </c>
-      <c r="B28" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C28" s="2">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="D28" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="E28" s="2">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F28" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="4"/>
-      <c r="B29" s="4"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="4"/>
-      <c r="E29" s="4"/>
-      <c r="F29" s="4"/>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A29" s="2"/>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="2"/>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:F29"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="14.88"/>
+    <col min="1" max="1" width="14.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1144,411 +1224,575 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="B2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
+      <c r="C2" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2">
+        <v>2</v>
+      </c>
+      <c r="E2" s="2">
+        <v>3</v>
+      </c>
       <c r="F2" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
-        <v>2.0</v>
-      </c>
-      <c r="B3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
+      <c r="C3" s="2">
+        <v>3</v>
+      </c>
+      <c r="D3" s="2">
+        <v>3</v>
+      </c>
+      <c r="E3" s="2">
+        <v>1</v>
+      </c>
       <c r="F3" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="B4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
+      <c r="C4" s="2">
+        <v>2</v>
+      </c>
+      <c r="D4" s="2">
+        <v>1</v>
+      </c>
+      <c r="E4" s="2">
+        <v>2</v>
+      </c>
       <c r="F4" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="B5" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
+      <c r="C5" s="2">
+        <v>1</v>
+      </c>
+      <c r="D5" s="2">
+        <v>3</v>
+      </c>
+      <c r="E5" s="2">
+        <v>1</v>
+      </c>
       <c r="F5" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="B6" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
+      <c r="C6" s="2">
+        <v>3</v>
+      </c>
+      <c r="D6" s="2">
+        <v>2</v>
+      </c>
+      <c r="E6" s="2">
+        <v>2</v>
+      </c>
       <c r="F6" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="B7" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
+      <c r="C7" s="2">
+        <v>2</v>
+      </c>
+      <c r="D7" s="2">
+        <v>3</v>
+      </c>
+      <c r="E7" s="2">
+        <v>1</v>
+      </c>
       <c r="F7" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
-        <v>7.0</v>
-      </c>
-      <c r="B8" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
+      <c r="C8" s="2">
+        <v>1</v>
+      </c>
+      <c r="D8" s="2">
+        <v>1</v>
+      </c>
+      <c r="E8" s="2">
+        <v>3</v>
+      </c>
       <c r="F8" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
-        <v>8.0</v>
-      </c>
-      <c r="B9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
+      <c r="C9" s="2">
+        <v>3</v>
+      </c>
+      <c r="D9" s="2">
+        <v>1</v>
+      </c>
+      <c r="E9" s="2">
+        <v>2</v>
+      </c>
       <c r="F9" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
-        <v>9.0</v>
-      </c>
-      <c r="B10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
+      <c r="C10" s="2">
+        <v>2</v>
+      </c>
+      <c r="D10" s="2">
+        <v>2</v>
+      </c>
+      <c r="E10" s="2">
+        <v>3</v>
+      </c>
       <c r="F10" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
-        <v>10.0</v>
-      </c>
-      <c r="B11" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
+      <c r="C11" s="2">
+        <v>1</v>
+      </c>
+      <c r="D11" s="2">
+        <v>2</v>
+      </c>
+      <c r="E11" s="2">
+        <v>1</v>
+      </c>
       <c r="F11" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
-        <v>11.0</v>
-      </c>
-      <c r="B12" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
+      <c r="C12" s="2">
+        <v>3</v>
+      </c>
+      <c r="D12" s="2">
+        <v>3</v>
+      </c>
+      <c r="E12" s="2">
+        <v>2</v>
+      </c>
       <c r="F12" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
-        <v>12.0</v>
-      </c>
-      <c r="B13" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
+      <c r="C13" s="2">
+        <v>2</v>
+      </c>
+      <c r="D13" s="2">
+        <v>1</v>
+      </c>
+      <c r="E13" s="2">
+        <v>1</v>
+      </c>
       <c r="F13" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
-        <v>13.0</v>
-      </c>
-      <c r="B14" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
+      <c r="C14" s="2">
+        <v>1</v>
+      </c>
+      <c r="D14" s="2">
+        <v>3</v>
+      </c>
+      <c r="E14" s="2">
+        <v>3</v>
+      </c>
       <c r="F14" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
-        <v>14.0</v>
-      </c>
-      <c r="B15" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
+      <c r="C15" s="2">
+        <v>3</v>
+      </c>
+      <c r="D15" s="2">
+        <v>2</v>
+      </c>
+      <c r="E15" s="2">
+        <v>3</v>
+      </c>
       <c r="F15" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
-        <v>15.0</v>
-      </c>
-      <c r="B16" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
+      <c r="C16" s="2">
+        <v>2</v>
+      </c>
+      <c r="D16" s="2">
+        <v>3</v>
+      </c>
+      <c r="E16" s="2">
+        <v>2</v>
+      </c>
       <c r="F16" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
-        <v>16.0</v>
-      </c>
-      <c r="B17" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
+      <c r="C17" s="2">
+        <v>1</v>
+      </c>
+      <c r="D17" s="2">
+        <v>1</v>
+      </c>
+      <c r="E17" s="2">
+        <v>1</v>
+      </c>
       <c r="F17" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
-        <v>17.0</v>
-      </c>
-      <c r="B18" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
+      <c r="C18" s="2">
+        <v>3</v>
+      </c>
+      <c r="D18" s="2">
+        <v>1</v>
+      </c>
+      <c r="E18" s="2">
+        <v>3</v>
+      </c>
       <c r="F18" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
-        <v>18.0</v>
-      </c>
-      <c r="B19" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
+      <c r="C19" s="2">
+        <v>2</v>
+      </c>
+      <c r="D19" s="2">
+        <v>2</v>
+      </c>
+      <c r="E19" s="2">
+        <v>2</v>
+      </c>
       <c r="F19" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
-        <v>19.0</v>
-      </c>
-      <c r="B20" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
+      <c r="C20" s="2">
+        <v>1</v>
+      </c>
+      <c r="D20" s="2">
+        <v>2</v>
+      </c>
+      <c r="E20" s="2">
+        <v>2</v>
+      </c>
       <c r="F20" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
-        <v>20.0</v>
-      </c>
-      <c r="B21" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4"/>
+      <c r="C21" s="2">
+        <v>3</v>
+      </c>
+      <c r="D21" s="2">
+        <v>3</v>
+      </c>
+      <c r="E21" s="2">
+        <v>3</v>
+      </c>
       <c r="F21" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
-        <v>21.0</v>
-      </c>
-      <c r="B22" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C22" s="4"/>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
+      <c r="C22" s="2">
+        <v>2</v>
+      </c>
+      <c r="D22" s="2">
+        <v>1</v>
+      </c>
+      <c r="E22" s="2">
+        <v>3</v>
+      </c>
       <c r="F22" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
-        <v>22.0</v>
-      </c>
-      <c r="B23" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B23" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4"/>
+      <c r="C23" s="2">
+        <v>1</v>
+      </c>
+      <c r="D23" s="2">
+        <v>3</v>
+      </c>
+      <c r="E23" s="2">
+        <v>2</v>
+      </c>
       <c r="F23" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
-        <v>23.0</v>
-      </c>
-      <c r="B24" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C24" s="4"/>
-      <c r="D24" s="4"/>
-      <c r="E24" s="4"/>
+      <c r="C24" s="2">
+        <v>3</v>
+      </c>
+      <c r="D24" s="2">
+        <v>2</v>
+      </c>
+      <c r="E24" s="2">
+        <v>1</v>
+      </c>
       <c r="F24" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
-        <v>24.0</v>
-      </c>
-      <c r="B25" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B25" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C25" s="4"/>
-      <c r="D25" s="4"/>
-      <c r="E25" s="4"/>
+      <c r="C25" s="2">
+        <v>2</v>
+      </c>
+      <c r="D25" s="2">
+        <v>3</v>
+      </c>
+      <c r="E25" s="2">
+        <v>3</v>
+      </c>
       <c r="F25" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
-        <v>25.0</v>
-      </c>
-      <c r="B26" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C26" s="4"/>
-      <c r="D26" s="4"/>
-      <c r="E26" s="4"/>
+      <c r="C26" s="2">
+        <v>1</v>
+      </c>
+      <c r="D26" s="2">
+        <v>1</v>
+      </c>
+      <c r="E26" s="2">
+        <v>2</v>
+      </c>
       <c r="F26" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27" s="2">
-        <v>26.0</v>
-      </c>
-      <c r="B27" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C27" s="4"/>
-      <c r="D27" s="4"/>
-      <c r="E27" s="4"/>
+      <c r="C27" s="2">
+        <v>3</v>
+      </c>
+      <c r="D27" s="2">
+        <v>1</v>
+      </c>
+      <c r="E27" s="2">
+        <v>1</v>
+      </c>
       <c r="F27" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28" s="2">
-        <v>27.0</v>
-      </c>
-      <c r="B28" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C28" s="4"/>
-      <c r="D28" s="4"/>
-      <c r="E28" s="4"/>
+      <c r="C28" s="2">
+        <v>2</v>
+      </c>
+      <c r="D28" s="2">
+        <v>2</v>
+      </c>
+      <c r="E28" s="2">
+        <v>1</v>
+      </c>
       <c r="F28" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="4"/>
-      <c r="B29" s="4"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="4"/>
-      <c r="E29" s="4"/>
-      <c r="F29" s="4"/>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A29" s="2"/>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="2"/>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:F29"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="14.88"/>
+    <col min="1" max="1" width="14.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1568,411 +1812,575 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="B2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
+      <c r="C2" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2" s="2">
+        <v>2</v>
+      </c>
+      <c r="E2" s="2">
+        <v>3</v>
+      </c>
       <c r="F2" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
-        <v>2.0</v>
-      </c>
-      <c r="B3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
+      <c r="C3" s="2">
+        <v>1</v>
+      </c>
+      <c r="D3" s="2">
+        <v>1</v>
+      </c>
+      <c r="E3" s="2">
+        <v>2</v>
+      </c>
       <c r="F3" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="B4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
+      <c r="C4" s="2">
+        <v>2</v>
+      </c>
+      <c r="D4" s="2">
+        <v>3</v>
+      </c>
+      <c r="E4" s="2">
+        <v>1</v>
+      </c>
       <c r="F4" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="B5" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
+      <c r="C5" s="2">
+        <v>3</v>
+      </c>
+      <c r="D5" s="2">
+        <v>3</v>
+      </c>
+      <c r="E5" s="2">
+        <v>1</v>
+      </c>
       <c r="F5" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="B6" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
+      <c r="C6" s="2">
+        <v>1</v>
+      </c>
+      <c r="D6" s="2">
+        <v>2</v>
+      </c>
+      <c r="E6" s="2">
+        <v>3</v>
+      </c>
       <c r="F6" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="B7" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
+      <c r="C7" s="2">
+        <v>2</v>
+      </c>
+      <c r="D7" s="2">
+        <v>1</v>
+      </c>
+      <c r="E7" s="2">
+        <v>2</v>
+      </c>
       <c r="F7" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
-        <v>7.0</v>
-      </c>
-      <c r="B8" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
+      <c r="C8" s="2">
+        <v>3</v>
+      </c>
+      <c r="D8" s="2">
+        <v>1</v>
+      </c>
+      <c r="E8" s="2">
+        <v>2</v>
+      </c>
       <c r="F8" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
-        <v>8.0</v>
-      </c>
-      <c r="B9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
+      <c r="C9" s="2">
+        <v>1</v>
+      </c>
+      <c r="D9" s="2">
+        <v>3</v>
+      </c>
+      <c r="E9" s="2">
+        <v>1</v>
+      </c>
       <c r="F9" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
-        <v>9.0</v>
-      </c>
-      <c r="B10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
+      <c r="C10" s="2">
+        <v>2</v>
+      </c>
+      <c r="D10" s="2">
+        <v>2</v>
+      </c>
+      <c r="E10" s="2">
+        <v>3</v>
+      </c>
       <c r="F10" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
-        <v>10.0</v>
-      </c>
-      <c r="B11" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
+      <c r="C11" s="2">
+        <v>3</v>
+      </c>
+      <c r="D11" s="2">
+        <v>2</v>
+      </c>
+      <c r="E11" s="2">
+        <v>2</v>
+      </c>
       <c r="F11" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
-        <v>11.0</v>
-      </c>
-      <c r="B12" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
+      <c r="C12" s="2">
+        <v>1</v>
+      </c>
+      <c r="D12" s="2">
+        <v>1</v>
+      </c>
+      <c r="E12" s="2">
+        <v>3</v>
+      </c>
       <c r="F12" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
-        <v>12.0</v>
-      </c>
-      <c r="B13" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
+      <c r="C13" s="2">
+        <v>2</v>
+      </c>
+      <c r="D13" s="2">
+        <v>3</v>
+      </c>
+      <c r="E13" s="2">
+        <v>2</v>
+      </c>
       <c r="F13" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
-        <v>13.0</v>
-      </c>
-      <c r="B14" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
+      <c r="C14" s="2">
+        <v>3</v>
+      </c>
+      <c r="D14" s="2">
+        <v>3</v>
+      </c>
+      <c r="E14" s="2">
+        <v>3</v>
+      </c>
       <c r="F14" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
-        <v>14.0</v>
-      </c>
-      <c r="B15" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
+      <c r="C15" s="2">
+        <v>1</v>
+      </c>
+      <c r="D15" s="2">
+        <v>2</v>
+      </c>
+      <c r="E15" s="2">
+        <v>1</v>
+      </c>
       <c r="F15" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
-        <v>15.0</v>
-      </c>
-      <c r="B16" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
+      <c r="C16" s="2">
+        <v>2</v>
+      </c>
+      <c r="D16" s="2">
+        <v>1</v>
+      </c>
+      <c r="E16" s="2">
+        <v>3</v>
+      </c>
       <c r="F16" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
-        <v>16.0</v>
-      </c>
-      <c r="B17" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
+      <c r="C17" s="2">
+        <v>3</v>
+      </c>
+      <c r="D17" s="2">
+        <v>1</v>
+      </c>
+      <c r="E17" s="2">
+        <v>1</v>
+      </c>
       <c r="F17" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
-        <v>17.0</v>
-      </c>
-      <c r="B18" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
+      <c r="C18" s="2">
+        <v>1</v>
+      </c>
+      <c r="D18" s="2">
+        <v>3</v>
+      </c>
+      <c r="E18" s="2">
+        <v>2</v>
+      </c>
       <c r="F18" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
-        <v>18.0</v>
-      </c>
-      <c r="B19" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
+      <c r="C19" s="2">
+        <v>2</v>
+      </c>
+      <c r="D19" s="2">
+        <v>2</v>
+      </c>
+      <c r="E19" s="2">
+        <v>1</v>
+      </c>
       <c r="F19" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
-        <v>19.0</v>
-      </c>
-      <c r="B20" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
+      <c r="C20" s="2">
+        <v>3</v>
+      </c>
+      <c r="D20" s="2">
+        <v>2</v>
+      </c>
+      <c r="E20" s="2">
+        <v>1</v>
+      </c>
       <c r="F20" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
-        <v>20.0</v>
-      </c>
-      <c r="B21" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4"/>
+      <c r="C21" s="2">
+        <v>1</v>
+      </c>
+      <c r="D21" s="2">
+        <v>1</v>
+      </c>
+      <c r="E21" s="2">
+        <v>1</v>
+      </c>
       <c r="F21" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
-        <v>21.0</v>
-      </c>
-      <c r="B22" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C22" s="4"/>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
+      <c r="C22" s="2">
+        <v>2</v>
+      </c>
+      <c r="D22" s="2">
+        <v>3</v>
+      </c>
+      <c r="E22" s="2">
+        <v>3</v>
+      </c>
       <c r="F22" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
-        <v>22.0</v>
-      </c>
-      <c r="B23" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B23" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4"/>
+      <c r="C23" s="2">
+        <v>3</v>
+      </c>
+      <c r="D23" s="2">
+        <v>3</v>
+      </c>
+      <c r="E23" s="2">
+        <v>2</v>
+      </c>
       <c r="F23" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
-        <v>23.0</v>
-      </c>
-      <c r="B24" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C24" s="4"/>
-      <c r="D24" s="4"/>
-      <c r="E24" s="4"/>
+      <c r="C24" s="2">
+        <v>1</v>
+      </c>
+      <c r="D24" s="2">
+        <v>2</v>
+      </c>
+      <c r="E24" s="2">
+        <v>2</v>
+      </c>
       <c r="F24" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
-        <v>24.0</v>
-      </c>
-      <c r="B25" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B25" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C25" s="4"/>
-      <c r="D25" s="4"/>
-      <c r="E25" s="4"/>
+      <c r="C25" s="2">
+        <v>2</v>
+      </c>
+      <c r="D25" s="2">
+        <v>1</v>
+      </c>
+      <c r="E25" s="2">
+        <v>1</v>
+      </c>
       <c r="F25" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
-        <v>25.0</v>
-      </c>
-      <c r="B26" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C26" s="4"/>
-      <c r="D26" s="4"/>
-      <c r="E26" s="4"/>
+      <c r="C26" s="2">
+        <v>3</v>
+      </c>
+      <c r="D26" s="2">
+        <v>1</v>
+      </c>
+      <c r="E26" s="2">
+        <v>3</v>
+      </c>
       <c r="F26" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27" s="2">
-        <v>26.0</v>
-      </c>
-      <c r="B27" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C27" s="4"/>
-      <c r="D27" s="4"/>
-      <c r="E27" s="4"/>
+      <c r="C27" s="2">
+        <v>1</v>
+      </c>
+      <c r="D27" s="2">
+        <v>3</v>
+      </c>
+      <c r="E27" s="2">
+        <v>3</v>
+      </c>
       <c r="F27" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28" s="2">
-        <v>27.0</v>
-      </c>
-      <c r="B28" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C28" s="4"/>
-      <c r="D28" s="4"/>
-      <c r="E28" s="4"/>
+      <c r="C28" s="2">
+        <v>2</v>
+      </c>
+      <c r="D28" s="2">
+        <v>2</v>
+      </c>
+      <c r="E28" s="2">
+        <v>2</v>
+      </c>
       <c r="F28" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="4"/>
-      <c r="B29" s="4"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="4"/>
-      <c r="E29" s="4"/>
-      <c r="F29" s="4"/>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A29" s="2"/>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="2"/>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:F29"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="14.88"/>
+    <col min="1" max="1" width="14.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1992,411 +2400,575 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="B2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
+      <c r="C2" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2" s="2">
+        <v>3</v>
+      </c>
+      <c r="E2" s="2">
+        <v>1</v>
+      </c>
       <c r="F2" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
-        <v>2.0</v>
-      </c>
-      <c r="B3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
+      <c r="C3" s="2">
+        <v>3</v>
+      </c>
+      <c r="D3" s="2">
+        <v>1</v>
+      </c>
+      <c r="E3" s="2">
+        <v>3</v>
+      </c>
       <c r="F3" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="B4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
+      <c r="C4" s="2">
+        <v>1</v>
+      </c>
+      <c r="D4" s="2">
+        <v>2</v>
+      </c>
+      <c r="E4" s="2">
+        <v>1</v>
+      </c>
       <c r="F4" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="B5" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
+      <c r="C5" s="2">
+        <v>2</v>
+      </c>
+      <c r="D5" s="2">
+        <v>2</v>
+      </c>
+      <c r="E5" s="2">
+        <v>2</v>
+      </c>
       <c r="F5" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="B6" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
+      <c r="C6" s="2">
+        <v>3</v>
+      </c>
+      <c r="D6" s="2">
+        <v>3</v>
+      </c>
+      <c r="E6" s="2">
+        <v>2</v>
+      </c>
       <c r="F6" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="B7" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
+      <c r="C7" s="2">
+        <v>1</v>
+      </c>
+      <c r="D7" s="2">
+        <v>1</v>
+      </c>
+      <c r="E7" s="2">
+        <v>3</v>
+      </c>
       <c r="F7" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
-        <v>7.0</v>
-      </c>
-      <c r="B8" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
+      <c r="C8" s="2">
+        <v>2</v>
+      </c>
+      <c r="D8" s="2">
+        <v>1</v>
+      </c>
+      <c r="E8" s="2">
+        <v>2</v>
+      </c>
       <c r="F8" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
-        <v>8.0</v>
-      </c>
-      <c r="B9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
+      <c r="C9" s="2">
+        <v>3</v>
+      </c>
+      <c r="D9" s="2">
+        <v>2</v>
+      </c>
+      <c r="E9" s="2">
+        <v>3</v>
+      </c>
       <c r="F9" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
-        <v>9.0</v>
-      </c>
-      <c r="B10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
+      <c r="C10" s="2">
+        <v>1</v>
+      </c>
+      <c r="D10" s="2">
+        <v>3</v>
+      </c>
+      <c r="E10" s="2">
+        <v>2</v>
+      </c>
       <c r="F10" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
-        <v>10.0</v>
-      </c>
-      <c r="B11" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
+      <c r="C11" s="2">
+        <v>2</v>
+      </c>
+      <c r="D11" s="2">
+        <v>3</v>
+      </c>
+      <c r="E11" s="2">
+        <v>3</v>
+      </c>
       <c r="F11" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
-        <v>11.0</v>
-      </c>
-      <c r="B12" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
+      <c r="C12" s="2">
+        <v>3</v>
+      </c>
+      <c r="D12" s="2">
+        <v>1</v>
+      </c>
+      <c r="E12" s="2">
+        <v>1</v>
+      </c>
       <c r="F12" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
-        <v>12.0</v>
-      </c>
-      <c r="B13" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
+      <c r="B13" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" s="2">
+        <v>1</v>
+      </c>
+      <c r="D13" s="2">
+        <v>2</v>
+      </c>
+      <c r="E13" s="2">
+        <v>3</v>
+      </c>
       <c r="F13" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
-        <v>13.0</v>
-      </c>
-      <c r="B14" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
+      <c r="C14" s="2">
+        <v>2</v>
+      </c>
+      <c r="D14" s="2">
+        <v>2</v>
+      </c>
+      <c r="E14" s="2">
+        <v>1</v>
+      </c>
       <c r="F14" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
-        <v>14.0</v>
-      </c>
-      <c r="B15" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
+      <c r="C15" s="2">
+        <v>3</v>
+      </c>
+      <c r="D15" s="2">
+        <v>3</v>
+      </c>
+      <c r="E15" s="2">
+        <v>1</v>
+      </c>
       <c r="F15" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
-        <v>15.0</v>
-      </c>
-      <c r="B16" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
+      <c r="C16" s="2">
+        <v>1</v>
+      </c>
+      <c r="D16" s="2">
+        <v>1</v>
+      </c>
+      <c r="E16" s="2">
+        <v>1</v>
+      </c>
       <c r="F16" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
-        <v>16.0</v>
-      </c>
-      <c r="B17" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
+      <c r="C17" s="2">
+        <v>2</v>
+      </c>
+      <c r="D17" s="2">
+        <v>1</v>
+      </c>
+      <c r="E17" s="2">
+        <v>3</v>
+      </c>
       <c r="F17" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
-        <v>17.0</v>
-      </c>
-      <c r="B18" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
+      <c r="C18" s="2">
+        <v>3</v>
+      </c>
+      <c r="D18" s="2">
+        <v>2</v>
+      </c>
+      <c r="E18" s="2">
+        <v>2</v>
+      </c>
       <c r="F18" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
-        <v>18.0</v>
-      </c>
-      <c r="B19" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
+      <c r="C19" s="2">
+        <v>1</v>
+      </c>
+      <c r="D19" s="2">
+        <v>3</v>
+      </c>
+      <c r="E19" s="2">
+        <v>3</v>
+      </c>
       <c r="F19" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
-        <v>19.0</v>
-      </c>
-      <c r="B20" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
+      <c r="C20" s="2">
+        <v>2</v>
+      </c>
+      <c r="D20" s="2">
+        <v>3</v>
+      </c>
+      <c r="E20" s="2">
+        <v>2</v>
+      </c>
       <c r="F20" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
-        <v>20.0</v>
-      </c>
-      <c r="B21" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4"/>
+      <c r="C21" s="2">
+        <v>3</v>
+      </c>
+      <c r="D21" s="2">
+        <v>1</v>
+      </c>
+      <c r="E21" s="2">
+        <v>2</v>
+      </c>
       <c r="F21" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
-        <v>21.0</v>
-      </c>
-      <c r="B22" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C22" s="4"/>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
+      <c r="C22" s="2">
+        <v>1</v>
+      </c>
+      <c r="D22" s="2">
+        <v>2</v>
+      </c>
+      <c r="E22" s="2">
+        <v>2</v>
+      </c>
       <c r="F22" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
-        <v>22.0</v>
-      </c>
-      <c r="B23" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B23" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4"/>
+      <c r="C23" s="2">
+        <v>2</v>
+      </c>
+      <c r="D23" s="2">
+        <v>2</v>
+      </c>
+      <c r="E23" s="2">
+        <v>3</v>
+      </c>
       <c r="F23" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
-        <v>23.0</v>
-      </c>
-      <c r="B24" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C24" s="4"/>
-      <c r="D24" s="4"/>
-      <c r="E24" s="4"/>
+      <c r="C24" s="2">
+        <v>3</v>
+      </c>
+      <c r="D24" s="2">
+        <v>3</v>
+      </c>
+      <c r="E24" s="2">
+        <v>3</v>
+      </c>
       <c r="F24" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
-        <v>24.0</v>
-      </c>
-      <c r="B25" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B25" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C25" s="4"/>
-      <c r="D25" s="4"/>
-      <c r="E25" s="4"/>
+      <c r="C25" s="2">
+        <v>1</v>
+      </c>
+      <c r="D25" s="2">
+        <v>1</v>
+      </c>
+      <c r="E25" s="2">
+        <v>2</v>
+      </c>
       <c r="F25" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
-        <v>25.0</v>
-      </c>
-      <c r="B26" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C26" s="4"/>
-      <c r="D26" s="4"/>
-      <c r="E26" s="4"/>
+      <c r="C26" s="2">
+        <v>2</v>
+      </c>
+      <c r="D26" s="2">
+        <v>1</v>
+      </c>
+      <c r="E26" s="2">
+        <v>1</v>
+      </c>
       <c r="F26" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27" s="2">
-        <v>26.0</v>
-      </c>
-      <c r="B27" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C27" s="4"/>
-      <c r="D27" s="4"/>
-      <c r="E27" s="4"/>
+      <c r="C27" s="2">
+        <v>3</v>
+      </c>
+      <c r="D27" s="2">
+        <v>2</v>
+      </c>
+      <c r="E27" s="2">
+        <v>1</v>
+      </c>
       <c r="F27" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28" s="2">
-        <v>27.0</v>
-      </c>
-      <c r="B28" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C28" s="4"/>
-      <c r="D28" s="4"/>
-      <c r="E28" s="4"/>
+      <c r="C28" s="2">
+        <v>1</v>
+      </c>
+      <c r="D28" s="2">
+        <v>3</v>
+      </c>
+      <c r="E28" s="2">
+        <v>1</v>
+      </c>
       <c r="F28" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="4"/>
-      <c r="B29" s="4"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="4"/>
-      <c r="E29" s="4"/>
-      <c r="F29" s="4"/>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A29" s="2"/>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="2"/>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:F29"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="14.88"/>
+    <col min="1" max="1" width="14.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2416,396 +2988,559 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="B2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
+      <c r="C2" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2" s="2">
+        <v>1</v>
+      </c>
+      <c r="E2" s="2">
+        <v>3</v>
+      </c>
       <c r="F2" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
-        <v>2.0</v>
-      </c>
-      <c r="B3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
+      <c r="C3" s="2">
+        <v>1</v>
+      </c>
+      <c r="D3" s="2">
+        <v>3</v>
+      </c>
+      <c r="E3" s="2">
+        <v>1</v>
+      </c>
       <c r="F3" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="B4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
+      <c r="C4" s="2">
+        <v>2</v>
+      </c>
+      <c r="D4" s="2">
+        <v>2</v>
+      </c>
+      <c r="E4" s="2">
+        <v>3</v>
+      </c>
       <c r="F4" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="B5" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
+      <c r="C5" s="2">
+        <v>3</v>
+      </c>
+      <c r="D5" s="2">
+        <v>3</v>
+      </c>
+      <c r="E5" s="2">
+        <v>2</v>
+      </c>
       <c r="F5" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="B6" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
+      <c r="C6" s="2">
+        <v>1</v>
+      </c>
+      <c r="D6" s="2">
+        <v>1</v>
+      </c>
+      <c r="E6" s="2">
+        <v>2</v>
+      </c>
       <c r="F6" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="B7" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
+      <c r="C7" s="2">
+        <v>2</v>
+      </c>
+      <c r="D7" s="2">
+        <v>1</v>
+      </c>
+      <c r="E7" s="2">
+        <v>1</v>
+      </c>
       <c r="F7" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
-        <v>7.0</v>
-      </c>
-      <c r="B8" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
+      <c r="C8" s="2">
+        <v>3</v>
+      </c>
+      <c r="D8" s="2">
+        <v>2</v>
+      </c>
+      <c r="E8" s="2">
+        <v>3</v>
+      </c>
       <c r="F8" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
-        <v>8.0</v>
-      </c>
-      <c r="B9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
+      <c r="C9" s="2">
+        <v>1</v>
+      </c>
+      <c r="D9" s="2">
+        <v>2</v>
+      </c>
+      <c r="E9" s="2">
+        <v>1</v>
+      </c>
       <c r="F9" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
-        <v>9.0</v>
-      </c>
-      <c r="B10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
+      <c r="C10" s="2">
+        <v>2</v>
+      </c>
+      <c r="D10" s="2">
+        <v>3</v>
+      </c>
+      <c r="E10" s="2">
+        <v>2</v>
+      </c>
       <c r="F10" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
-        <v>10.0</v>
-      </c>
-      <c r="B11" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
+      <c r="C11" s="2">
+        <v>3</v>
+      </c>
+      <c r="D11" s="2">
+        <v>1</v>
+      </c>
+      <c r="E11" s="2">
+        <v>1</v>
+      </c>
       <c r="F11" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
-        <v>11.0</v>
-      </c>
-      <c r="B12" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
+      <c r="C12" s="2">
+        <v>1</v>
+      </c>
+      <c r="D12" s="2">
+        <v>3</v>
+      </c>
+      <c r="E12" s="2">
+        <v>3</v>
+      </c>
       <c r="F12" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
-        <v>12.0</v>
-      </c>
-      <c r="B13" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
+      <c r="C13" s="2">
+        <v>2</v>
+      </c>
+      <c r="D13" s="2">
+        <v>2</v>
+      </c>
+      <c r="E13" s="2">
+        <v>1</v>
+      </c>
       <c r="F13" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
-        <v>13.0</v>
-      </c>
-      <c r="B14" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
+      <c r="B14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C14" s="2">
+        <v>3</v>
+      </c>
+      <c r="D14" s="2">
+        <v>3</v>
+      </c>
+      <c r="E14" s="2">
+        <v>1</v>
+      </c>
       <c r="F14" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
-        <v>14.0</v>
-      </c>
-      <c r="B15" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
+      <c r="C15" s="2">
+        <v>1</v>
+      </c>
+      <c r="D15" s="2">
+        <v>1</v>
+      </c>
+      <c r="E15" s="2">
+        <v>3</v>
+      </c>
       <c r="F15" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
-        <v>15.0</v>
-      </c>
-      <c r="B16" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
+      <c r="C16" s="2">
+        <v>2</v>
+      </c>
+      <c r="D16" s="2">
+        <v>1</v>
+      </c>
+      <c r="E16" s="2">
+        <v>2</v>
+      </c>
       <c r="F16" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
-        <v>16.0</v>
-      </c>
-      <c r="B17" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
+      <c r="C17" s="2">
+        <v>3</v>
+      </c>
+      <c r="D17" s="2">
+        <v>2</v>
+      </c>
+      <c r="E17" s="2">
+        <v>2</v>
+      </c>
       <c r="F17" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
-        <v>17.0</v>
-      </c>
-      <c r="B18" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
+      <c r="C18" s="2">
+        <v>1</v>
+      </c>
+      <c r="D18" s="2">
+        <v>2</v>
+      </c>
+      <c r="E18" s="2">
+        <v>3</v>
+      </c>
       <c r="F18" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
-        <v>18.0</v>
-      </c>
-      <c r="B19" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
+      <c r="C19" s="2">
+        <v>2</v>
+      </c>
+      <c r="D19" s="2">
+        <v>3</v>
+      </c>
+      <c r="E19" s="2">
+        <v>1</v>
+      </c>
       <c r="F19" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
-        <v>19.0</v>
-      </c>
-      <c r="B20" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
+      <c r="B20" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C20" s="2">
+        <v>3</v>
+      </c>
+      <c r="D20" s="2">
+        <v>1</v>
+      </c>
+      <c r="E20" s="2">
+        <v>2</v>
+      </c>
       <c r="F20" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
-        <v>20.0</v>
-      </c>
-      <c r="B21" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4"/>
+      <c r="C21" s="2">
+        <v>1</v>
+      </c>
+      <c r="D21" s="2">
+        <v>3</v>
+      </c>
+      <c r="E21" s="2">
+        <v>2</v>
+      </c>
       <c r="F21" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
-        <v>21.0</v>
-      </c>
-      <c r="B22" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="4"/>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
+      <c r="C22" s="2">
+        <v>2</v>
+      </c>
+      <c r="D22" s="2">
+        <v>2</v>
+      </c>
+      <c r="E22" s="2">
+        <v>3</v>
+      </c>
       <c r="F22" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
-        <v>22.0</v>
-      </c>
-      <c r="B23" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4"/>
+      <c r="B23" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C23" s="2">
+        <v>3</v>
+      </c>
+      <c r="D23" s="2">
+        <v>3</v>
+      </c>
+      <c r="E23" s="2">
+        <v>3</v>
+      </c>
       <c r="F23" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
-        <v>23.0</v>
-      </c>
-      <c r="B24" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C24" s="4"/>
-      <c r="D24" s="4"/>
-      <c r="E24" s="4"/>
+      <c r="C24" s="2">
+        <v>1</v>
+      </c>
+      <c r="D24" s="2">
+        <v>1</v>
+      </c>
+      <c r="E24" s="2">
+        <v>1</v>
+      </c>
       <c r="F24" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
-        <v>24.0</v>
-      </c>
-      <c r="B25" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B25" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C25" s="4"/>
-      <c r="D25" s="4"/>
-      <c r="E25" s="4"/>
+      <c r="C25" s="2">
+        <v>2</v>
+      </c>
+      <c r="D25" s="2">
+        <v>1</v>
+      </c>
+      <c r="E25" s="2">
+        <v>3</v>
+      </c>
       <c r="F25" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
-        <v>25.0</v>
-      </c>
-      <c r="B26" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C26" s="4"/>
-      <c r="D26" s="4"/>
-      <c r="E26" s="4"/>
+      <c r="C26" s="2">
+        <v>3</v>
+      </c>
+      <c r="D26" s="2">
+        <v>2</v>
+      </c>
+      <c r="E26" s="2">
+        <v>1</v>
+      </c>
       <c r="F26" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27" s="2">
-        <v>26.0</v>
-      </c>
-      <c r="B27" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C27" s="4"/>
-      <c r="D27" s="4"/>
-      <c r="E27" s="4"/>
+      <c r="C27" s="2">
+        <v>1</v>
+      </c>
+      <c r="D27" s="2">
+        <v>2</v>
+      </c>
+      <c r="E27" s="2">
+        <v>2</v>
+      </c>
       <c r="F27" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28" s="2">
-        <v>27.0</v>
-      </c>
-      <c r="B28" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C28" s="4"/>
-      <c r="D28" s="4"/>
-      <c r="E28" s="4"/>
+      <c r="C28" s="2">
+        <v>2</v>
+      </c>
+      <c r="D28" s="2">
+        <v>3</v>
+      </c>
+      <c r="E28" s="2">
+        <v>3</v>
+      </c>
       <c r="F28" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="4"/>
-      <c r="B29" s="4"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="4"/>
-      <c r="E29" s="4"/>
-      <c r="F29" s="4"/>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A29" s="2"/>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="2"/>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>